--- a/exports/DRREDDY_full_report.xlsx
+++ b/exports/DRREDDY_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q64"/>
+  <dimension ref="A1:U64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>3.1</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44581.55208333334</v>
+        <v>44582.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>919.4</v>
+        <v>905.2</v>
       </c>
       <c r="I2" t="n">
         <v>912.89368603475</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K2" t="n">
-        <v>-1.92</v>
+        <v>-3.44</v>
       </c>
       <c r="L2" t="n">
-        <v>2.5</v>
+        <v>5.38</v>
       </c>
       <c r="M2" t="n">
-        <v>0.44</v>
+        <v>0.78</v>
       </c>
       <c r="N2" t="n">
-        <v>1.71</v>
+        <v>2.08</v>
       </c>
       <c r="O2" t="n">
         <v>-0.19</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>4.11</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44636.55208333334</v>
+        <v>44637.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>785.5</v>
+        <v>804</v>
       </c>
       <c r="I3" t="n">
         <v>800.8279826991845</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>54.16666666666666</v>
+        <v>55</v>
       </c>
       <c r="K3" t="n">
-        <v>13.22</v>
+        <v>11.18</v>
       </c>
       <c r="L3" t="n">
         <v>0.8100000000000001</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>74</v>
+        <v>75</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>6.58</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44670.38541666666</v>
+        <v>44670.55208333334</v>
       </c>
       <c r="H4" t="n">
-        <v>848.6</v>
+        <v>839.85</v>
       </c>
       <c r="I4" t="n">
         <v>842.1113840577357</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>33</v>
+        <v>33.16666666666666</v>
       </c>
       <c r="K4" t="n">
-        <v>5.55</v>
+        <v>4.46</v>
       </c>
       <c r="L4" t="n">
         <v>1.82</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>5.79</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44700.55208333334</v>
+        <v>44701.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>788.45</v>
+        <v>848</v>
       </c>
       <c r="I5" t="n">
         <v>809.5788086065165</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>30</v>
+        <v>30.83333333333333</v>
       </c>
       <c r="K5" t="n">
-        <v>6.12</v>
+        <v>-0.97</v>
       </c>
       <c r="L5" t="n">
         <v>3.62</v>
@@ -726,7 +785,7 @@
         <v>1.2</v>
       </c>
       <c r="N5" t="n">
-        <v>2.33</v>
+        <v>7.25</v>
       </c>
       <c r="O5" t="n">
         <v>-1.68</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,28 +833,28 @@
         <v>10.16</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44718.55208333334</v>
+        <v>44719.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>857.3</v>
+        <v>834.55</v>
       </c>
       <c r="I6" t="n">
         <v>834.6445714191586</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K6" t="n">
-        <v>1.1</v>
+        <v>-1.59</v>
       </c>
       <c r="L6" t="n">
         <v>6.25</v>
       </c>
       <c r="M6" t="n">
-        <v>0.39</v>
+        <v>0.62</v>
       </c>
       <c r="N6" t="n">
-        <v>0.95</v>
+        <v>3.42</v>
       </c>
       <c r="O6" t="n">
         <v>7.25</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>5.53</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44740.38541666666</v>
+        <v>44740.55208333334</v>
       </c>
       <c r="H7" t="n">
-        <v>868.5</v>
+        <v>875</v>
       </c>
       <c r="I7" t="n">
         <v>872.4543660227009</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>21</v>
+        <v>21.16666666666667</v>
       </c>
       <c r="K7" t="n">
-        <v>-4.07</v>
+        <v>-4.85</v>
       </c>
       <c r="L7" t="n">
         <v>5.44</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>4.98</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44764.55208333334</v>
+        <v>44767.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>875.4</v>
+        <v>867.8</v>
       </c>
       <c r="I8" t="n">
         <v>869.4450171425453</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>24</v>
+        <v>26.83333333333333</v>
       </c>
       <c r="K8" t="n">
-        <v>0.05</v>
+        <v>-0.82</v>
       </c>
       <c r="L8" t="n">
         <v>1.94</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>4.62</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44784.55208333334</v>
+        <v>44785.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>851.2</v>
+        <v>855.4</v>
       </c>
       <c r="I9" t="n">
         <v>852.0214841731021</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K9" t="n">
-        <v>1.91</v>
+        <v>1.43</v>
       </c>
       <c r="L9" t="n">
         <v>1.16</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>4</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44792.38541666666</v>
+        <v>44792.55208333334</v>
       </c>
       <c r="H10" t="n">
-        <v>844</v>
+        <v>837.6</v>
       </c>
       <c r="I10" t="n">
         <v>837.7542032911209</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>7</v>
+        <v>7.166666666666667</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.33</v>
+        <v>-2.08</v>
       </c>
       <c r="L10" t="n">
         <v>3.31</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>4.22</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44824.38541666666</v>
+        <v>44824.55208333334</v>
       </c>
       <c r="H11" t="n">
-        <v>834.9</v>
+        <v>843.45</v>
       </c>
       <c r="I11" t="n">
         <v>842.4168679503704</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>31.83333333333333</v>
+        <v>32</v>
       </c>
       <c r="K11" t="n">
-        <v>0.32</v>
+        <v>-0.7</v>
       </c>
       <c r="L11" t="n">
         <v>3.14</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>4.35</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44883.55208333334</v>
+        <v>44886.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>880.5</v>
+        <v>869.45</v>
       </c>
       <c r="I12" t="n">
         <v>872.8491261475381</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>59</v>
+        <v>61.83333333333334</v>
       </c>
       <c r="K12" t="n">
-        <v>4.39</v>
+        <v>3.08</v>
       </c>
       <c r="L12" t="n">
         <v>3.03</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>80</v>
+        <v>81</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>4.98</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44909.38541666666</v>
+        <v>44909.55208333334</v>
       </c>
       <c r="H13" t="n">
-        <v>898.7</v>
+        <v>901.2</v>
       </c>
       <c r="I13" t="n">
         <v>899.1884379121166</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>23</v>
+        <v>23.16666666666667</v>
       </c>
       <c r="K13" t="n">
-        <v>-3.36</v>
+        <v>-3.65</v>
       </c>
       <c r="L13" t="n">
         <v>4.25</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>3.6</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44916.55208333334</v>
+        <v>44917.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>882.6</v>
+        <v>868.15</v>
       </c>
       <c r="I14" t="n">
         <v>869.0005903536917</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>7</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="K14" t="n">
-        <v>-2.06</v>
+        <v>-3.67</v>
       </c>
       <c r="L14" t="n">
         <v>5.39</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>5.57</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44958.38541666666</v>
+        <v>44958.55208333334</v>
       </c>
       <c r="H15" t="n">
-        <v>864.55</v>
+        <v>870</v>
       </c>
       <c r="I15" t="n">
         <v>868.0022860036951</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>41</v>
+        <v>41.16666666666666</v>
       </c>
       <c r="K15" t="n">
-        <v>0.41</v>
+        <v>-0.21</v>
       </c>
       <c r="L15" t="n">
         <v>2.63</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>4.25</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44984.55208333334</v>
+        <v>44985.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>882.2</v>
+        <v>876.2</v>
       </c>
       <c r="I16" t="n">
         <v>877.1870299547322</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>26</v>
+        <v>26.83333333333333</v>
       </c>
       <c r="K16" t="n">
-        <v>1.4</v>
+        <v>0.71</v>
       </c>
       <c r="L16" t="n">
         <v>1.49</v>
@@ -1353,7 +1544,7 @@
         <v>0.89</v>
       </c>
       <c r="N16" t="n">
-        <v>1.76</v>
+        <v>2.2</v>
       </c>
       <c r="O16" t="n">
         <v>0.46</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,25 +1592,25 @@
         <v>4.35</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>45009.55208333334</v>
+        <v>45012.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>891</v>
+        <v>898.8</v>
       </c>
       <c r="I17" t="n">
         <v>898.6845809555773</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>27</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.69</v>
+        <v>-2.58</v>
       </c>
       <c r="L17" t="n">
-        <v>2.7</v>
+        <v>3.37</v>
       </c>
       <c r="M17" t="n">
-        <v>0.63</v>
+        <v>0.79</v>
       </c>
       <c r="N17" t="n">
         <v>1.73</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S17" t="b">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1446,28 +1661,28 @@
         <v>3.2</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>45056.55208333334</v>
+        <v>45057.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>973.8</v>
+        <v>909.4</v>
       </c>
       <c r="I18" t="n">
         <v>964.2352750095552</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>44.16666666666666</v>
+        <v>45</v>
       </c>
       <c r="K18" t="n">
-        <v>8.34</v>
+        <v>1.18</v>
       </c>
       <c r="L18" t="n">
         <v>0.65</v>
       </c>
       <c r="M18" t="n">
-        <v>0.5600000000000001</v>
+        <v>3.98</v>
       </c>
       <c r="N18" t="n">
-        <v>1.52</v>
+        <v>6.96</v>
       </c>
       <c r="O18" t="n">
         <v>0.7</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>7.19</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45078.55208333334</v>
+        <v>45079.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>910</v>
+        <v>921.55</v>
       </c>
       <c r="I19" t="n">
         <v>913.5401369888189</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-1.34</v>
       </c>
       <c r="L19" t="n">
         <v>3.36</v>
@@ -1524,7 +1751,7 @@
         <v>0.43</v>
       </c>
       <c r="N19" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="O19" t="n">
         <v>-6.96</v>
@@ -1533,7 +1760,19 @@
         <v>1</v>
       </c>
       <c r="Q19" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>3.18</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45163.38541666666</v>
+        <v>45163.55208333334</v>
       </c>
       <c r="H20" t="n">
-        <v>1164.7</v>
+        <v>1157</v>
       </c>
       <c r="I20" t="n">
         <v>1157.85829816758</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>84</v>
+        <v>84.16666666666667</v>
       </c>
       <c r="K20" t="n">
-        <v>26.38</v>
+        <v>25.55</v>
       </c>
       <c r="L20" t="n">
         <v>0.9</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>117</v>
+        <v>118</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3</v>
+      </c>
+      <c r="U20" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -1617,28 +1868,28 @@
         <v>3.73</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45183.55208333334</v>
+        <v>45184.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>1147.6</v>
+        <v>1156</v>
       </c>
       <c r="I21" t="n">
         <v>1149.615231954423</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>20</v>
+        <v>20.83333333333333</v>
       </c>
       <c r="K21" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="L21" t="n">
         <v>1</v>
       </c>
       <c r="M21" t="n">
-        <v>0.53</v>
+        <v>0.67</v>
       </c>
       <c r="N21" t="n">
-        <v>1.59</v>
+        <v>1.73</v>
       </c>
       <c r="O21" t="n">
         <v>-2.31</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,22 +1937,22 @@
         <v>3.34</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45189.38541666666</v>
+        <v>45189.55208333334</v>
       </c>
       <c r="H22" t="n">
-        <v>1133.25</v>
+        <v>1122</v>
       </c>
       <c r="I22" t="n">
         <v>1125.330167753922</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>5</v>
+        <v>5.166666666666667</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.97</v>
+        <v>-2.94</v>
       </c>
       <c r="L22" t="n">
-        <v>2.47</v>
+        <v>3.08</v>
       </c>
       <c r="M22" t="n">
         <v>0.28</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S22" t="b">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>3.89</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45216.55208333334</v>
+        <v>45217.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>1108</v>
+        <v>1132.4</v>
       </c>
       <c r="I23" t="n">
         <v>1123.555944663051</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>27</v>
+        <v>27.83333333333333</v>
       </c>
       <c r="K23" t="n">
-        <v>1.25</v>
+        <v>-0.93</v>
       </c>
       <c r="L23" t="n">
         <v>1.55</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,28 +2075,28 @@
         <v>4.27</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45224.55208333334</v>
+        <v>45225.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>1101.9</v>
+        <v>1073</v>
       </c>
       <c r="I24" t="n">
         <v>1097.969290132437</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K24" t="n">
-        <v>-2.69</v>
+        <v>-5.25</v>
       </c>
       <c r="L24" t="n">
-        <v>2.86</v>
+        <v>5.32</v>
       </c>
       <c r="M24" t="n">
         <v>0.8</v>
       </c>
       <c r="N24" t="n">
-        <v>0.95</v>
+        <v>1.55</v>
       </c>
       <c r="O24" t="n">
         <v>2.26</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S24" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>5.49</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45245.55208333334</v>
+        <v>45246.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>1083</v>
+        <v>1101.55</v>
       </c>
       <c r="I25" t="n">
         <v>1098.458448940587</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.93</v>
+        <v>-2.66</v>
       </c>
       <c r="L25" t="n">
         <v>2.84</v>
@@ -1866,7 +2165,7 @@
         <v>0.75</v>
       </c>
       <c r="N25" t="n">
-        <v>1.32</v>
+        <v>2.23</v>
       </c>
       <c r="O25" t="n">
         <v>-1.55</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S25" t="b">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1902,28 +2213,28 @@
         <v>4.2</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45268.55208333334</v>
+        <v>45271.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>1153.6</v>
+        <v>1089.95</v>
       </c>
       <c r="I26" t="n">
         <v>1120.375115711972</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K26" t="n">
-        <v>4.73</v>
+        <v>-1.05</v>
       </c>
       <c r="L26" t="n">
-        <v>1.58</v>
+        <v>2.5</v>
       </c>
       <c r="M26" t="n">
-        <v>0.17</v>
+        <v>4.65</v>
       </c>
       <c r="N26" t="n">
-        <v>0.66</v>
+        <v>5.07</v>
       </c>
       <c r="O26" t="n">
         <v>2.23</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,28 +2282,28 @@
         <v>5.86</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45287.55208333334</v>
+        <v>45288.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>1143</v>
+        <v>1148.55</v>
       </c>
       <c r="I27" t="n">
         <v>1147.088401825897</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K27" t="n">
-        <v>-4.87</v>
+        <v>-5.38</v>
       </c>
       <c r="L27" t="n">
-        <v>5</v>
+        <v>5.91</v>
       </c>
       <c r="M27" t="n">
         <v>0.48</v>
       </c>
       <c r="N27" t="n">
-        <v>1.51</v>
+        <v>2.24</v>
       </c>
       <c r="O27" t="n">
         <v>-5.07</v>
@@ -1989,7 +2312,19 @@
         <v>1</v>
       </c>
       <c r="Q27" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S27" t="b">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2016,28 +2351,28 @@
         <v>4.1</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45301.55208333334</v>
+        <v>45302.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>1158.6</v>
+        <v>1134.8</v>
       </c>
       <c r="I28" t="n">
         <v>1145.45439917422</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K28" t="n">
-        <v>0.88</v>
+        <v>-1.2</v>
       </c>
       <c r="L28" t="n">
-        <v>1.25</v>
+        <v>1.7</v>
       </c>
       <c r="M28" t="n">
-        <v>0.22</v>
+        <v>0.26</v>
       </c>
       <c r="N28" t="n">
-        <v>1.56</v>
+        <v>1.64</v>
       </c>
       <c r="O28" t="n">
         <v>2.24</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S28" t="b">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2073,28 +2420,28 @@
         <v>4.91</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45314.55208333334</v>
+        <v>45315.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>1136.4</v>
+        <v>1172</v>
       </c>
       <c r="I29" t="n">
         <v>1167.074741669945</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.14</v>
+        <v>-3.28</v>
       </c>
       <c r="L29" t="n">
-        <v>2.2</v>
+        <v>4.12</v>
       </c>
       <c r="M29" t="n">
         <v>0.8100000000000001</v>
       </c>
       <c r="N29" t="n">
-        <v>1.62</v>
+        <v>3.68</v>
       </c>
       <c r="O29" t="n">
         <v>-1.64</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>5.59</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45370.38541666666</v>
+        <v>45370.55208333334</v>
       </c>
       <c r="H30" t="n">
-        <v>1241</v>
+        <v>1227.4</v>
       </c>
       <c r="I30" t="n">
         <v>1239.705595025901</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>55</v>
+        <v>55.16666666666666</v>
       </c>
       <c r="K30" t="n">
-        <v>5.89</v>
+        <v>4.73</v>
       </c>
       <c r="L30" t="n">
         <v>2.85</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>74</v>
+        <v>75</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>4.61</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45407.38541666666</v>
+        <v>45407.55208333334</v>
       </c>
       <c r="H31" t="n">
-        <v>1205</v>
+        <v>1250</v>
       </c>
       <c r="I31" t="n">
         <v>1233.911119517664</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>36.83333333333334</v>
+        <v>37</v>
       </c>
       <c r="K31" t="n">
-        <v>1.82</v>
+        <v>-1.84</v>
       </c>
       <c r="L31" t="n">
         <v>2.75</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,28 +2627,28 @@
         <v>6.35</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45419.55208333334</v>
+        <v>45420.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>1254.7</v>
+        <v>1209.6</v>
       </c>
       <c r="I32" t="n">
         <v>1217.663833579094</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>12</v>
+        <v>12.83333333333333</v>
       </c>
       <c r="K32" t="n">
-        <v>0.38</v>
+        <v>-3.23</v>
       </c>
       <c r="L32" t="n">
-        <v>3.68</v>
+        <v>4.76</v>
       </c>
       <c r="M32" t="n">
-        <v>0.4</v>
+        <v>2.77</v>
       </c>
       <c r="N32" t="n">
-        <v>1.13</v>
+        <v>3.51</v>
       </c>
       <c r="O32" t="n">
         <v>4.88</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S32" t="b">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>5.71</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45449.55208333334</v>
+        <v>45450.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>1179.9</v>
+        <v>1209.75</v>
       </c>
       <c r="I33" t="n">
         <v>1204.321413255319</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>30</v>
       </c>
       <c r="K33" t="n">
-        <v>2.46</v>
+        <v>-0.01</v>
       </c>
       <c r="L33" t="n">
         <v>1.11</v>
@@ -2322,7 +2717,7 @@
         <v>2.7</v>
       </c>
       <c r="N33" t="n">
-        <v>1.43</v>
+        <v>2.56</v>
       </c>
       <c r="O33" t="n">
         <v>-3.51</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>6.71</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45538.55208333334</v>
+        <v>45539.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>1370</v>
+        <v>1356.25</v>
       </c>
       <c r="I34" t="n">
         <v>1367.711414996079</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>88.16666666666667</v>
+        <v>89</v>
       </c>
       <c r="K34" t="n">
-        <v>13.25</v>
+        <v>12.11</v>
       </c>
       <c r="L34" t="n">
         <v>2.85</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>120</v>
+        <v>121</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>4</v>
+      </c>
+      <c r="U34" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>3.92</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45560.55208333334</v>
+        <v>45561.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>1340</v>
+        <v>1343.8</v>
       </c>
       <c r="I35" t="n">
         <v>1340.900808202393</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K35" t="n">
-        <v>1.2</v>
+        <v>0.92</v>
       </c>
       <c r="L35" t="n">
         <v>1</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S35" t="b">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,22 +2903,22 @@
         <v>3.5</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45589.55208333334</v>
+        <v>45590.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>1317.1</v>
+        <v>1300.4</v>
       </c>
       <c r="I36" t="n">
         <v>1310.47368708094</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>29</v>
       </c>
       <c r="K36" t="n">
-        <v>-1.99</v>
+        <v>-3.23</v>
       </c>
       <c r="L36" t="n">
-        <v>2.59</v>
+        <v>4</v>
       </c>
       <c r="M36" t="n">
         <v>0.39</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S36" t="b">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>4.02</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45631.55208333334</v>
+        <v>45632.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>1242</v>
+        <v>1251.9</v>
       </c>
       <c r="I37" t="n">
         <v>1251.760661413698</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>41.16666666666666</v>
+        <v>42</v>
       </c>
       <c r="K37" t="n">
-        <v>4.49</v>
+        <v>3.73</v>
       </c>
       <c r="L37" t="n">
         <v>2.69</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>3</v>
+      </c>
+      <c r="U37" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>4.57</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45672.55208333334</v>
+        <v>45673.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>1333.5</v>
+        <v>1301.9</v>
       </c>
       <c r="I38" t="n">
         <v>1326.083530815409</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>40.16666666666666</v>
+        <v>41</v>
       </c>
       <c r="K38" t="n">
-        <v>6.52</v>
+        <v>3.99</v>
       </c>
       <c r="L38" t="n">
         <v>2.04</v>
@@ -2607,7 +3062,7 @@
         <v>0.63</v>
       </c>
       <c r="N38" t="n">
-        <v>1.65</v>
+        <v>1.99</v>
       </c>
       <c r="O38" t="n">
         <v>0.93</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>6.9</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45729.55208333334</v>
+        <v>45733.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>1106</v>
+        <v>1145.15</v>
       </c>
       <c r="I39" t="n">
         <v>1144.169238550371</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>56.16666666666666</v>
+        <v>60</v>
       </c>
       <c r="K39" t="n">
-        <v>15.05</v>
+        <v>12.04</v>
       </c>
       <c r="L39" t="n">
         <v>3.46</v>
@@ -2664,7 +3131,7 @@
         <v>0.82</v>
       </c>
       <c r="N39" t="n">
-        <v>1.63</v>
+        <v>4.11</v>
       </c>
       <c r="O39" t="n">
         <v>-1.99</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>82</v>
+        <v>83</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3</v>
+      </c>
+      <c r="U39" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -2700,25 +3179,25 @@
         <v>6.17</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45742.55208333334</v>
+        <v>45743.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>1161.4</v>
+        <v>1154</v>
       </c>
       <c r="I40" t="n">
         <v>1158.806167923209</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K40" t="n">
-        <v>1.42</v>
+        <v>0.77</v>
       </c>
       <c r="L40" t="n">
         <v>3.81</v>
       </c>
       <c r="M40" t="n">
-        <v>0.02</v>
+        <v>0.12</v>
       </c>
       <c r="N40" t="n">
         <v>2.86</v>
@@ -2730,7 +3209,19 @@
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S40" t="b">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>4.61</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45763.55208333334</v>
+        <v>45764.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>1150.9</v>
+        <v>1167.6</v>
       </c>
       <c r="I41" t="n">
         <v>1162.797565568003</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K41" t="n">
-        <v>0.27</v>
+        <v>-1.18</v>
       </c>
       <c r="L41" t="n">
         <v>6.32</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>7.13</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45825.55208333334</v>
+        <v>45826.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>1319</v>
+        <v>1315.3</v>
       </c>
       <c r="I42" t="n">
         <v>1317.105714196561</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>61.16666666666666</v>
+        <v>62</v>
       </c>
       <c r="K42" t="n">
-        <v>12.97</v>
+        <v>12.65</v>
       </c>
       <c r="L42" t="n">
         <v>3.27</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>3</v>
+      </c>
+      <c r="U42" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>4.3</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45866.38541666666</v>
+        <v>45866.55208333334</v>
       </c>
       <c r="H43" t="n">
-        <v>1279.1</v>
+        <v>1287</v>
       </c>
       <c r="I43" t="n">
         <v>1280.191400906205</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>40</v>
+        <v>40.16666666666666</v>
       </c>
       <c r="K43" t="n">
-        <v>2.75</v>
+        <v>2.15</v>
       </c>
       <c r="L43" t="n">
         <v>2.92</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -2928,28 +3455,28 @@
         <v>4.06</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45869.55208333334</v>
+        <v>45870.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>1267.1</v>
+        <v>1221</v>
       </c>
       <c r="I44" t="n">
         <v>1249.341809239523</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>3</v>
+        <v>3.833333333333333</v>
       </c>
       <c r="K44" t="n">
-        <v>-1.55</v>
+        <v>-5.13</v>
       </c>
       <c r="L44" t="n">
-        <v>2.33</v>
+        <v>5.53</v>
       </c>
       <c r="M44" t="n">
         <v>1.35</v>
       </c>
       <c r="N44" t="n">
-        <v>1.93</v>
+        <v>3.61</v>
       </c>
       <c r="O44" t="n">
         <v>0.78</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>6.49</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45881.55208333334</v>
+        <v>45882.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>1218.7</v>
+        <v>1250.3</v>
       </c>
       <c r="I45" t="n">
         <v>1245.854471905495</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>12</v>
       </c>
       <c r="K45" t="n">
-        <v>0.19</v>
+        <v>-2.4</v>
       </c>
       <c r="L45" t="n">
         <v>3.11</v>
@@ -3006,7 +3545,7 @@
         <v>0.3</v>
       </c>
       <c r="N45" t="n">
-        <v>1.25</v>
+        <v>2.85</v>
       </c>
       <c r="O45" t="n">
         <v>-3.61</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S45" t="b">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>5.67</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45924.55208333334</v>
+        <v>45925.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>1298</v>
+        <v>1271.7</v>
       </c>
       <c r="I46" t="n">
         <v>1283.313773727838</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>42.16666666666666</v>
+        <v>43</v>
       </c>
       <c r="K46" t="n">
-        <v>3.82</v>
+        <v>1.71</v>
       </c>
       <c r="L46" t="n">
         <v>2.44</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>4.9</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45947.55208333334</v>
+        <v>45950.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>1256.6</v>
+        <v>1282.9</v>
       </c>
       <c r="I47" t="n">
         <v>1273.592078630134</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K47" t="n">
-        <v>1.19</v>
+        <v>-0.88</v>
       </c>
       <c r="L47" t="n">
         <v>2.8</v>
@@ -3120,7 +3683,7 @@
         <v>0.86</v>
       </c>
       <c r="N47" t="n">
-        <v>1.71</v>
+        <v>2.26</v>
       </c>
       <c r="O47" t="n">
         <v>-1.8</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,28 +3731,28 @@
         <v>4.35</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45959.55208333334</v>
+        <v>45960.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>1258.4</v>
+        <v>1206.1</v>
       </c>
       <c r="I48" t="n">
         <v>1247.221050320232</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K48" t="n">
-        <v>-1.91</v>
+        <v>-5.99</v>
       </c>
       <c r="L48" t="n">
-        <v>3.73</v>
+        <v>7.95</v>
       </c>
       <c r="M48" t="n">
-        <v>0.15</v>
+        <v>4.96</v>
       </c>
       <c r="N48" t="n">
-        <v>2.74</v>
+        <v>4.36</v>
       </c>
       <c r="O48" t="n">
         <v>2.26</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,22 +3800,22 @@
         <v>5.41</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45974.55208333334</v>
+        <v>45975.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>1234.4</v>
+        <v>1245.3</v>
       </c>
       <c r="I49" t="n">
         <v>1243.7863886129</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K49" t="n">
-        <v>-2.35</v>
+        <v>-3.25</v>
       </c>
       <c r="L49" t="n">
-        <v>3.01</v>
+        <v>3.47</v>
       </c>
       <c r="M49" t="n">
         <v>0.59</v>
@@ -3243,7 +3830,19 @@
         <v>1</v>
       </c>
       <c r="Q49" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S49" t="b">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>3.72</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>46027.38541666666</v>
+        <v>46027.55208333334</v>
       </c>
       <c r="H50" t="n">
-        <v>1260.4</v>
+        <v>1247.1</v>
       </c>
       <c r="I50" t="n">
         <v>1247.48662823401</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>52</v>
+        <v>52.16666666666666</v>
       </c>
       <c r="K50" t="n">
-        <v>1.21</v>
+        <v>0.14</v>
       </c>
       <c r="L50" t="n">
         <v>2.11</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>71</v>
+        <v>72</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>3</v>
+      </c>
+      <c r="U50" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -3327,28 +3938,28 @@
         <v>3.52</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>46043.55208333334</v>
+        <v>46044.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>1156</v>
+        <v>1220.2</v>
       </c>
       <c r="I51" t="n">
         <v>1212.465835702442</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>16</v>
+        <v>16.83333333333333</v>
       </c>
       <c r="K51" t="n">
-        <v>7.3</v>
+        <v>2.16</v>
       </c>
       <c r="L51" t="n">
         <v>1.44</v>
       </c>
       <c r="M51" t="n">
-        <v>0.27</v>
+        <v>3.37</v>
       </c>
       <c r="N51" t="n">
-        <v>0.63</v>
+        <v>5.42</v>
       </c>
       <c r="O51" t="n">
         <v>-0.83</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S51" t="b">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>7.04</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>46104.38541666666</v>
+        <v>46104.55208333334</v>
       </c>
       <c r="H52" t="n">
-        <v>1273.9</v>
+        <v>1248</v>
       </c>
       <c r="I52" t="n">
         <v>1261.993016111284</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>60</v>
+        <v>60.16666666666666</v>
       </c>
       <c r="K52" t="n">
-        <v>4.4</v>
+        <v>2.28</v>
       </c>
       <c r="L52" t="n">
         <v>4.35</v>
@@ -3414,7 +4037,19 @@
         <v>1</v>
       </c>
       <c r="Q52" t="n">
-        <v>83</v>
+        <v>84</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>3</v>
+      </c>
+      <c r="U52" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="53">
@@ -3441,28 +4076,28 @@
         <v>6.2</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>46134.55208333334</v>
+        <v>46135.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>1216.3</v>
+        <v>1321.6</v>
       </c>
       <c r="I53" t="n">
         <v>1266.887539948732</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>30</v>
+        <v>30.83333333333333</v>
       </c>
       <c r="K53" t="n">
-        <v>2.54</v>
+        <v>-5.9</v>
       </c>
       <c r="L53" t="n">
-        <v>4.89</v>
+        <v>5.93</v>
       </c>
       <c r="M53" t="n">
         <v>2.24</v>
       </c>
       <c r="N53" t="n">
-        <v>4.09</v>
+        <v>8.94</v>
       </c>
       <c r="O53" t="n">
         <v>-3.7</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>9.619999999999999</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>46154.38541666666</v>
+        <v>46154.55208333334</v>
       </c>
       <c r="H54" t="n">
-        <v>1279.9</v>
+        <v>1267.5</v>
       </c>
       <c r="I54" t="n">
         <v>1271.36949998986</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>19</v>
+        <v>19.16666666666667</v>
       </c>
       <c r="K54" t="n">
-        <v>-3.16</v>
+        <v>-4.09</v>
       </c>
       <c r="L54" t="n">
         <v>7.88</v>
@@ -3528,7 +4175,19 @@
         <v>1</v>
       </c>
       <c r="Q54" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,22 +4214,22 @@
         <v>5.83</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>46157.38541666666</v>
+        <v>46157.55208333334</v>
       </c>
       <c r="H55" t="n">
-        <v>1321.7</v>
+        <v>1343.3</v>
       </c>
       <c r="I55" t="n">
         <v>1341.409979920106</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>2.833333333333333</v>
+        <v>3</v>
       </c>
       <c r="K55" t="n">
-        <v>-4.28</v>
+        <v>-5.98</v>
       </c>
       <c r="L55" t="n">
-        <v>5.23</v>
+        <v>6.11</v>
       </c>
       <c r="M55" t="n">
         <v>0.18</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S55" t="b">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>1</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -3612,22 +4283,22 @@
         <v>7.2</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46175.55208333334</v>
+        <v>46176.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>1277</v>
+        <v>1262.9</v>
       </c>
       <c r="I56" t="n">
         <v>1271.034293781274</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>18</v>
+        <v>18.83333333333333</v>
       </c>
       <c r="K56" t="n">
-        <v>-4.94</v>
+        <v>-5.99</v>
       </c>
       <c r="L56" t="n">
-        <v>5.9</v>
+        <v>6.43</v>
       </c>
       <c r="M56" t="n">
         <v>0.78</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,28 +4352,28 @@
         <v>4.87</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46196.55208333334</v>
+        <v>46197.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>1300.9</v>
+        <v>1337.7</v>
       </c>
       <c r="I57" t="n">
         <v>1309.612762970067</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K57" t="n">
-        <v>-3.01</v>
+        <v>-5.92</v>
       </c>
       <c r="L57" t="n">
-        <v>5.27</v>
+        <v>6.34</v>
       </c>
       <c r="M57" t="n">
         <v>1.83</v>
       </c>
       <c r="N57" t="n">
-        <v>1.5</v>
+        <v>2.16</v>
       </c>
       <c r="O57" t="n">
         <v>-1.1</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S57" t="b">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>1</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -3726,28 +4421,28 @@
         <v>5.34</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46211.55208333334</v>
+        <v>46212.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>1351.1</v>
+        <v>1267.8</v>
       </c>
       <c r="I58" t="n">
         <v>1312.511543013621</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K58" t="n">
-        <v>1</v>
+        <v>-5.23</v>
       </c>
       <c r="L58" t="n">
-        <v>2.35</v>
+        <v>5.73</v>
       </c>
       <c r="M58" t="n">
-        <v>0.73</v>
+        <v>0.82</v>
       </c>
       <c r="N58" t="n">
-        <v>1.7</v>
+        <v>5.91</v>
       </c>
       <c r="O58" t="n">
         <v>2.16</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>9.9</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46244.55208333334</v>
+        <v>46245.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>1160</v>
+        <v>1195</v>
       </c>
       <c r="I59" t="n">
         <v>1193.585643444917</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>32.16666666666666</v>
+        <v>33</v>
       </c>
       <c r="K59" t="n">
-        <v>8.5</v>
+        <v>5.74</v>
       </c>
       <c r="L59" t="n">
         <v>6.4</v>
@@ -3804,7 +4511,7 @@
         <v>1.76</v>
       </c>
       <c r="N59" t="n">
-        <v>2.05</v>
+        <v>3.95</v>
       </c>
       <c r="O59" t="n">
         <v>-5.91</v>
@@ -3813,7 +4520,19 @@
         <v>1</v>
       </c>
       <c r="Q59" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>5.51</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46267.55208333334</v>
+        <v>46268.38541666666</v>
       </c>
       <c r="H60" t="n">
-        <v>1161.3</v>
+        <v>1157.3</v>
       </c>
       <c r="I60" t="n">
         <v>1159.946163798272</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>23</v>
       </c>
       <c r="K60" t="n">
-        <v>-2.82</v>
+        <v>-3.15</v>
       </c>
       <c r="L60" t="n">
         <v>3.34</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3897,28 +4628,28 @@
         <v>3.18</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46275.55208333334</v>
+        <v>46276.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>1141</v>
+        <v>1174.2</v>
       </c>
       <c r="I61" t="n">
         <v>1171.567674559711</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K61" t="n">
-        <v>1.41</v>
+        <v>-1.46</v>
       </c>
       <c r="L61" t="n">
-        <v>0.82</v>
+        <v>2.13</v>
       </c>
       <c r="M61" t="n">
         <v>0.06</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O61" t="n">
         <v>-0.27</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S61" t="b">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>1</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>5.17</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46302.55208333334</v>
+        <v>46303.38541666666</v>
       </c>
       <c r="H62" t="n">
-        <v>1200.5</v>
+        <v>1171.6</v>
       </c>
       <c r="I62" t="n">
         <v>1193.850332477747</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>26.16666666666667</v>
+        <v>27</v>
       </c>
       <c r="K62" t="n">
-        <v>2.24</v>
+        <v>-0.22</v>
       </c>
       <c r="L62" t="n">
         <v>3.76</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>2</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -4011,28 +4766,28 @@
         <v>5.74</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46304.55208333334</v>
+        <v>46307.38541666666</v>
       </c>
       <c r="H63" t="n">
-        <v>1197</v>
+        <v>1229.7</v>
       </c>
       <c r="I63" t="n">
         <v>1227.146976009222</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>1.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K63" t="n">
-        <v>-2.17</v>
+        <v>-4.96</v>
       </c>
       <c r="L63" t="n">
-        <v>2.53</v>
+        <v>5.14</v>
       </c>
       <c r="M63" t="n">
         <v>0.32</v>
       </c>
       <c r="N63" t="n">
-        <v>1.77</v>
+        <v>2.86</v>
       </c>
       <c r="O63" t="n">
         <v>-2.02</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S63" t="b">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>1</v>
+      </c>
+      <c r="U63" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -4092,6 +4859,14 @@
       <c r="Q64" t="n">
         <v>24</v>
       </c>
+      <c r="R64" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="inlineStr"/>
+      <c r="U64" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6194,7 +6969,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>27.1</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6">
@@ -6204,7 +6979,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>22.2</v>
+        <v>23.1</v>
       </c>
     </row>
     <row r="7">
@@ -6214,7 +6989,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>88.2</v>
+        <v>89</v>
       </c>
     </row>
     <row r="8">
@@ -6224,7 +6999,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -6234,7 +7009,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>35.9</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10">
@@ -6244,7 +7019,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>54.9</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="11">
@@ -6254,7 +7029,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="12">
@@ -6264,7 +7039,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13">
@@ -6274,7 +7049,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>69.40000000000001</v>
+        <v>66.09999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -6284,7 +7059,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.03</v>
+        <v>-0.09</v>
       </c>
     </row>
     <row r="15">
@@ -6294,7 +7069,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.57</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="16">
@@ -6304,7 +7079,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.49</v>
+        <v>-0.67</v>
       </c>
     </row>
     <row r="17">
@@ -6314,7 +7089,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>26.38</v>
+        <v>25.55</v>
       </c>
     </row>
     <row r="18">
@@ -6324,7 +7099,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>64.5</v>
+        <v>35.5</v>
       </c>
     </row>
     <row r="19">
@@ -6334,7 +7109,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.07</v>
+        <v>3.58</v>
       </c>
     </row>
     <row r="20">
@@ -6344,7 +7119,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.84</v>
+        <v>3.29</v>
       </c>
     </row>
     <row r="21">
@@ -6354,7 +7129,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>7.88</v>
+        <v>7.95</v>
       </c>
     </row>
     <row r="22">
@@ -6364,7 +7139,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
     </row>
     <row r="23">
@@ -6384,7 +7159,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.04</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="25">
@@ -6394,7 +7169,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4.27</v>
+        <v>4.96</v>
       </c>
     </row>
     <row r="26">
@@ -6404,7 +7179,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.04</v>
+        <v>2.92</v>
       </c>
     </row>
     <row r="27">
@@ -6414,7 +7189,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4.88</v>
+        <v>8.94</v>
       </c>
     </row>
     <row r="28">
@@ -6424,7 +7199,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29">
